--- a/materdata.xlsx
+++ b/materdata.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\Nhahang\projecthotel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TBCNVN\NhaHang\projecthotel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C47EFB4-2FF7-41B4-9BF3-3658B974184A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hanghoa" sheetId="2" r:id="rId1"/>
@@ -28,6 +29,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -476,9 +480,6 @@
     <t>tuananh</t>
   </si>
   <si>
-    <t>tu?n anh</t>
-  </si>
-  <si>
     <t>nhanvien1</t>
   </si>
   <si>
@@ -516,12 +517,15 @@
   </si>
   <si>
     <t>nồi</t>
+  </si>
+  <si>
+    <t>tuan anh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -845,7 +849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1030,7 +1034,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>15</v>
@@ -1114,7 +1118,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>2</v>
@@ -1156,7 +1160,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>2</v>
@@ -1198,7 +1202,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>2</v>
@@ -1240,7 +1244,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>2</v>
@@ -1282,10 +1286,10 @@
         <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -1324,10 +1328,10 @@
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -1366,7 +1370,7 @@
         <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>2</v>
@@ -1618,7 +1622,7 @@
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>45</v>
@@ -1660,7 +1664,7 @@
         <v>46</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>45</v>
@@ -1744,7 +1748,7 @@
         <v>49</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>50</v>
@@ -1800,7 +1804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2010,7 +2014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3074,9 +3078,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="20.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
@@ -3147,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -3205,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>4</v>
@@ -3258,7 +3265,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3407,7 +3414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3497,7 +3504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3768,7 +3775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3881,7 +3888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3938,7 +3945,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
